--- a/llm_stats/token_usage.xlsx
+++ b/llm_stats/token_usage.xlsx
@@ -8,6 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="Usage" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="PromptVersionSummary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ModelSummary" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,115 +416,777 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:AX3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Timestamp</t>
+          <t>run_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Problem Number</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Problem Name</t>
+          <t>problem_number</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>problem_name</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Prompt Tokens</t>
+          <t>problem_link</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Response Tokens</t>
+          <t>difficulty</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Total Tokens</t>
+          <t>language</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Total Duration (ms)</t>
+          <t>model</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Load Duration (ms)</t>
+          <t>prompt_version</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Prompt Eval Duration (ms)</t>
+          <t>prompt_strategy</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Generation Duration (ms)</t>
+          <t>prompt_hash</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Tokens/sec</t>
+          <t>prompt_preview</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prompt_text</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prompt_chars</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prompt_lines</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>code_chars</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>code_lines</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>code_sha256</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>code_text</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prompt_tokens</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>response_tokens</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>total_tokens</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>output_input_ratio</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>total_duration_ms</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>load_duration_ms</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prompt_eval_ms</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>generation_ms</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>tokens_per_sec</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>http_status</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>error_type</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>retry_count</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>timeout_flag</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>llm_returned_code_block</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>code_appended_externally</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>llm_response_chars</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>llm_response_lines</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>llm_response_text</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>response_chars</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>response_lines</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>has_title</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>has_intuition</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>has_approach</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>has_time_complexity</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>has_space_complexity</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>has_code_block</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>format_score</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>completeness_score</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>manual_edit_distance</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>accepted_for_posting</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>error_message</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-01 12:36:40</t>
+          <t>12a55ed2-5d4f-42a5-a520-69b9842c0200</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3370</t>
+          <t>2026-03-11 00:12:31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Smallest Number With All Set Bits</t>
+          <t>3793</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Find Users with High Token Usage</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>mistral</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>legacy</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>1510</v>
+      </c>
+      <c r="O2" t="n">
+        <v>69</v>
+      </c>
+      <c r="P2" t="n">
+        <v>424</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>19</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>517</v>
+      </c>
+      <c r="U2" t="n">
+        <v>549</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1066</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.0619</v>
+      </c>
+      <c r="X2" t="n">
+        <v>153606.67</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>8706.940000000001</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>42886.88</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>100512.77</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>5.462</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>200</v>
+      </c>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>46</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="AX2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>35d9ebf5-fd18-4133-9ae8-5fda9db93c69</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-11 11:33:26</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Construct Binary Tree from Preorder and Inorder Traversal</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>legacy</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>2355</v>
+      </c>
+      <c r="O3" t="n">
+        <v>85</v>
+      </c>
+      <c r="P3" t="n">
+        <v>812</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>27</v>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="n">
+        <v>762</v>
+      </c>
+      <c r="U3" t="n">
+        <v>717</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1479</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.9409</v>
+      </c>
+      <c r="X3" t="n">
+        <v>193847.33</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>5516.67</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>54975.12</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>132426.69</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>5.4143</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>200</v>
+      </c>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="n">
+        <v>2753</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>58</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>total_runs</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>success_runs</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>failed_runs</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>timeout_runs</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>avg_tokens_per_sec</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5.44</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>avg_total_duration_ms</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>173727</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>avg_completeness_score</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>91.66</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>avg_format_score</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>90</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>prompt_version</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>prompt_strategy</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>prompt_hash</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>runs</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>avg_completeness</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>avg_format</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>avg_tokens_per_sec</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>avg_output_input_ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>360</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>351</v>
+        <v>91.66</v>
       </c>
       <c r="G2" t="n">
-        <v>711</v>
+        <v>90</v>
       </c>
       <c r="H2" t="n">
-        <v>98932.3</v>
+        <v>5.44</v>
       </c>
       <c r="I2" t="n">
-        <v>6036.85</v>
-      </c>
-      <c r="J2" t="n">
-        <v>29767.4</v>
-      </c>
-      <c r="K2" t="n">
-        <v>62912.63</v>
-      </c>
-      <c r="L2" t="n">
-        <v>5.58</v>
+        <v>1.0014</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>runs</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>avg_tokens_per_sec</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>avg_duration_ms</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>avg_completeness</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="D2" t="n">
+        <v>173727</v>
+      </c>
+      <c r="E2" t="n">
+        <v>91.66</v>
       </c>
     </row>
   </sheetData>

--- a/llm_stats/token_usage.xlsx
+++ b/llm_stats/token_usage.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX7"/>
+  <dimension ref="A1:AX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1960,6 +1960,692 @@
       </c>
       <c r="AX7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>d30a2a88-986d-40ef-a051-cc94482a3ed2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-03-12 21:30:04</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3622</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Check Divisibility by Digit Sum and Product</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/problems/check-divisibility-by-digit-sum-and-product/description/</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>190d07deeba31923371931835131a7c933cda0cea82e762a7fb575ee0620409f</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>You are an expert technical writer creating a high-quality LeetCode solution post. Problem Details: Number: 3622 Name: Check Divisibility by Digit Sum and Product Difficulty: easy Link: https://leetcode.com/problems/check-divisibility-by-digit-sum-and-product/description/ Pyth...</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are an expert technical writer creating a high-quality LeetCode solution post.
+Problem Details:
+Number: 3622
+Name: Check Divisibility by Digit Sum and Product
+Difficulty: easy
+Link: https://leetcode.com/problems/check-divisibility-by-digit-sum-and-product/description/
+Python Solution:
+class Solution:
+    def checkDivisibility(self, n: int) -&gt; bool:
+        presDigitSum = 0
+        presDigitProduct = 1
+        originalNo = n
+        while n &gt; 0:
+            presDigit = n%10
+            presDigitSum += presDigit
+            presDigitProduct *= presDigit
+            n = n//10
+        return originalNo%(presDigitSum+presDigitProduct) == 0
+Instructions:
+1. Generate a strong, descriptive, professional Title.
+- The title MUST mention:
+    - The core technique used
+    - The time complexity (Big-O notation)
+- The explanation must match the provided language
+- IMPORTANT: The title text (after "Title: ") must be 75 characters or fewer.
+2. Generate markdown using exactly these sections and no additional top-level sections:
+Title: &lt;single line title, max 75 characters&gt;
+## Intuition
+## Approach
+## Time Complexity
+## Space Complexity
+3. Do NOT include any code block and do NOT add a ## Code section.
+4. Keep the response concise, technical, and ready for markdown publishing.
+</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>1302</v>
+      </c>
+      <c r="O8" t="n">
+        <v>42</v>
+      </c>
+      <c r="P8" t="n">
+        <v>366</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>13</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>be052ed46c2d8207e2a263b065073525ffce218711af2c625d5b3e6f4316532b</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>class Solution:
+    def checkDivisibility(self, n: int) -&gt; bool:
+        presDigitSum = 0
+        presDigitProduct = 1
+        originalNo = n
+        while n &gt; 0:
+            presDigit = n%10
+            presDigitSum += presDigit
+            presDigitProduct *= presDigit
+            n = n//10
+        return originalNo%(presDigitSum+presDigitProduct) == 0</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>379</v>
+      </c>
+      <c r="U8" t="n">
+        <v>327</v>
+      </c>
+      <c r="V8" t="n">
+        <v>706</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.8628</v>
+      </c>
+      <c r="X8" t="n">
+        <v>97439.44</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>8465.74</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>30790.23</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>57369.32</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>5.6999</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>200</v>
+      </c>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1372</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Title: Divisibility Check Using Digit Sum and Product in Python (O(log n))
+## Intuition
+The problem requires checking if a number `n` is divisible by the sum of its digits plus the product of its digits. The algorithm iteratively calculates both quantities as we traverse the number, comparing them to the original number at each step to determine divisibility.
+## Approach
+1. Initialize variables for storing the partial digit sum and product during traversal of the input number `n`.
+2. Iterate through each digit in the number from right to left. In each iteration:
+   - Add the current digit to the partial sum (`presDigitSum`).
+   - Multiply the partial product (`presDigitProduct`) by the current digit.
+   - Divide `n` by 10 to remove its least significant digit and use the result for the next iteration.
+3. Return True if the original number is divisible by the calculated sum and product, and False otherwise.
+## Time Complexity
+The time complexity of this solution is O(log n), since we traverse the input number logarithmically using integer division (//). The constant factor involved in this solution is relatively small due to minimal arithmetic operations per iteration.
+## Space Complexity
+The space complexity of this solution is O(1) as it uses only a few constants and variables, which do not increase based on the size of the input number `n`.</t>
+        </is>
+      </c>
+      <c r="AL8" t="n">
+        <v>1839</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>9adeffbb-cdd7-4e54-bb87-ec6d2e3abd36</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-03-12 21:31:12</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>704</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Binary Search</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/problems/binary-search/description/</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>4c1920be931a0e0f286bac0b10ab71359af3866862bfefe062950718493bd2e4</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>You are an expert technical writer creating a high-quality LeetCode solution post. Problem Details: Number: 704 Name: Binary Search Difficulty: easy Link: https://leetcode.com/problems/binary-search/description/ Python Solution: import bisect class Solution: def search(self, n...</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are an expert technical writer creating a high-quality LeetCode solution post.
+Problem Details:
+Number: 704
+Name: Binary Search
+Difficulty: easy
+Link: https://leetcode.com/problems/binary-search/description/
+Python Solution:
+import bisect
+class Solution:
+    def search(self, nums: List[int], target: int) -&gt; int:
+        index = bisect.bisect_left(nums,target)
+        if index &lt; len(nums):
+            if nums[index] == target:
+                return index
+        return -1
+Instructions:
+1. Generate a strong, descriptive, professional Title.
+- The title MUST mention:
+    - The core technique used
+    - The time complexity (Big-O notation)
+- The explanation must match the provided language
+- IMPORTANT: The title text (after "Title: ") must be 75 characters or fewer.
+2. Generate markdown using exactly these sections and no additional top-level sections:
+Title: &lt;single line title, max 75 characters&gt;
+## Intuition
+## Approach
+## Time Complexity
+## Space Complexity
+3. Do NOT include any code block and do NOT add a ## Code section.
+4. Keep the response concise, technical, and ready for markdown publishing.
+</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>1129</v>
+      </c>
+      <c r="O9" t="n">
+        <v>40</v>
+      </c>
+      <c r="P9" t="n">
+        <v>254</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>11</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>e137afb35da73117914419ecea6d521e1c376640a9bf108fd31f9c25d0bfff60</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>import bisect
+class Solution:
+    def search(self, nums: List[int], target: int) -&gt; int:
+        index = bisect.bisect_left(nums,target)
+        if index &lt; len(nums):
+            if nums[index] == target:
+                return index
+        return -1</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>324</v>
+      </c>
+      <c r="U9" t="n">
+        <v>264</v>
+      </c>
+      <c r="V9" t="n">
+        <v>588</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.8148</v>
+      </c>
+      <c r="X9" t="n">
+        <v>165410.18</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>8464.709999999999</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>23870.55</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>43291.78</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>6.0982</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>200</v>
+      </c>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Title: Binary Search Using Bisect in Python - O(log n) Time Complexity
+## Intuition
+The binary search algorithm is a divide-and-conquer method used for finding an element within a sorted list by repeatedly dividing the search interval in half. This strategy makes it an efficient solution when dealing with large datasets.
+## Approach
+In this implementation, we utilize the built-in `bisect` module in Python to perform a binary search. The `bisect_left` function finds the insertion point for target in sorted list nums such that all elements before it are less than or equal to target. If the found index has a matching value with target, it is returned; otherwise, -1 is returned.
+## Time Complexity
+The time complexity of this approach is O(log n) because each comparison eliminates half of the remaining elements in the sorted list. This makes binary search one of the most efficient searching algorithms for large datasets.
+## Space Complexity
+In terms of space complexity, our solution requires only a constant amount of additional space (O(1)) for the `index` variable since it simply keeps track of the search progress without storing all intermediate values during the search process.</t>
+        </is>
+      </c>
+      <c r="AL9" t="n">
+        <v>1557</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>35</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>a877842e-dc7c-4d06-b988-654259a0d3b1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-03-12 21:32:51</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2236</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Root Equals Sum of Children</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/problems/root-equals-sum-of-children/description/</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>6f78255f768bfa5f0cae2b19b49b5e9ac4f4ccad222b54f97c0804076b85421e</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>You are an expert technical writer creating a high-quality LeetCode solution post. Problem Details: Number: 2236 Name: Root Equals Sum of Children Difficulty: easy Link: https://leetcode.com/problems/root-equals-sum-of-children/description/ Python Solution: # Definition for a ...</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are an expert technical writer creating a high-quality LeetCode solution post.
+Problem Details:
+Number: 2236
+Name: Root Equals Sum of Children
+Difficulty: easy
+Link: https://leetcode.com/problems/root-equals-sum-of-children/description/
+Python Solution:
+# Definition for a binary tree node.
+# class TreeNode:
+#     def __init__(self, val=0, left=None, right=None):
+#         self.val = val
+#         self.left = left
+#         self.right = right
+class Solution:
+    def checkTree(self, root: Optional[TreeNode]) -&gt; bool:
+        if not root:
+            return True
+        rootVal = root.val
+        leftVal, rightVal = 0,0
+        if root.left:
+            leftVal = root.left.val
+        if root.right:
+            rightVal = root.right.val
+        return rootVal == leftVal + rightVal
+Instructions:
+1. Generate a strong, descriptive, professional Title.
+- The title MUST mention:
+    - The core technique used
+    - The time complexity (Big-O notation)
+- The explanation must match the provided language
+- IMPORTANT: The title text (after "Title: ") must be 75 characters or fewer.
+2. Generate markdown using exactly these sections and no additional top-level sections:
+Title: &lt;single line title, max 75 characters&gt;
+## Intuition
+## Approach
+## Time Complexity
+## Space Complexity
+3. Do NOT include any code block and do NOT add a ## Code section.
+4. Keep the response concise, technical, and ready for markdown publishing.
+</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>1450</v>
+      </c>
+      <c r="O10" t="n">
+        <v>50</v>
+      </c>
+      <c r="P10" t="n">
+        <v>546</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>21</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>788ab863539fc469928f080678dccaa087cbb6071486d394a933156490bf5d20</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t># Definition for a binary tree node.
+# class TreeNode:
+#     def __init__(self, val=0, left=None, right=None):
+#         self.val = val
+#         self.left = left
+#         self.right = right
+class Solution:
+    def checkTree(self, root: Optional[TreeNode]) -&gt; bool:
+        if not root:
+            return True
+        rootVal = root.val
+        leftVal, rightVal = 0,0
+        if root.left:
+            leftVal = root.left.val
+        if root.right:
+            rightVal = root.right.val
+        return rootVal == leftVal + rightVal</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>416</v>
+      </c>
+      <c r="U10" t="n">
+        <v>349</v>
+      </c>
+      <c r="V10" t="n">
+        <v>765</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.8389</v>
+      </c>
+      <c r="X10" t="n">
+        <v>263537.47</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>8464.709999999999</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>32888.37</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>64436.57</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>5.4162</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>200</v>
+      </c>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1395</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Title: Depth-First Search Verification: O(N) Solution for LeetCode Problem 2236
+## Intuition
+The core technique employed in this solution is a depth-first search (DFS). The goal is to verify if the root value of a binary tree equals the sum of its children's values. We perform DFS on the tree to calculate the sum of both children recursively, then compare it with the root's value.
+## Approach
+Starting from the root node, we recursively traverse the binary tree using DFS. At each level (either left or right subtree), we calculate the sum of all nodes' values. When reaching the leaf nodes, we return the calculated sum as the sum of its children. Finally, we compare this sum with the root's value and check if they are equal. If yes, the tree satisfies the condition; otherwise, it does not.
+## Time Complexity
+The time complexity of our solution is O(N), where N is the number of nodes in the binary tree. This is due to the recursive nature of DFS, which visits each node only once.
+## Space Complexity
+The space complexity of this algorithm is O(H), where H is the height of the tree. We utilize the stack to store the recursion call frames during the DFS traversal, and the maximum depth reached in the traversal will define the stack's size. However, since it's a balanced binary tree, the height is logarithmic (O(log N)), hence the overall space complexity is also O(log N).</t>
+        </is>
+      </c>
+      <c r="AL10" t="n">
+        <v>2042</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>45</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1993,7 +2679,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -2003,7 +2689,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -2033,7 +2719,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.58</v>
+        <v>5.64</v>
       </c>
     </row>
     <row r="7">
@@ -2043,7 +2729,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>122902.86</v>
+        <v>140422.7</v>
       </c>
     </row>
     <row r="8">
@@ -2053,7 +2739,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>97.22</v>
+        <v>98.15000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -2063,7 +2749,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>96.67</v>
+        <v>97.78</v>
       </c>
     </row>
   </sheetData>
@@ -2077,7 +2763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2211,7 +2897,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4136b715d00f86dbecec596bc2b3edd9d641459ca344c6cf63430eeb8a8d0479</t>
+          <t>190d07deeba31923371931835131a7c933cda0cea82e762a7fb575ee0620409f</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -2224,10 +2910,10 @@
         <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>6.08</v>
+        <v>5.7</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1103</v>
+        <v>0.8628</v>
       </c>
     </row>
     <row r="5">
@@ -2248,7 +2934,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>bc4d6a1b30057aeb421828e3058b67b393c68ef3e9a044f87d681c404bd8d7c3</t>
+          <t>4136b715d00f86dbecec596bc2b3edd9d641459ca344c6cf63430eeb8a8d0479</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -2261,10 +2947,10 @@
         <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>6.31</v>
+        <v>6.08</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9457</v>
+        <v>1.1103</v>
       </c>
     </row>
     <row r="6">
@@ -2285,7 +2971,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>c0cf95285f54eaebedb9669a2aebe8239832722a8830a2e4215272d5a7af2264</t>
+          <t>4c1920be931a0e0f286bac0b10ab71359af3866862bfefe062950718493bd2e4</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -2298,9 +2984,120 @@
         <v>100</v>
       </c>
       <c r="H6" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.8148</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6f78255f768bfa5f0cae2b19b49b5e9ac4f4ccad222b54f97c0804076b85421e</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>100</v>
+      </c>
+      <c r="G7" t="n">
+        <v>100</v>
+      </c>
+      <c r="H7" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.8389</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>bc4d6a1b30057aeb421828e3058b67b393c68ef3e9a044f87d681c404bd8d7c3</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>100</v>
+      </c>
+      <c r="G8" t="n">
+        <v>100</v>
+      </c>
+      <c r="H8" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.9457</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>c0cf95285f54eaebedb9669a2aebe8239832722a8830a2e4215272d5a7af2264</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H9" t="n">
         <v>4.64</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I9" t="n">
         <v>1.1983</v>
       </c>
     </row>
@@ -2352,16 +3149,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>5.58</v>
+        <v>5.64</v>
       </c>
       <c r="D2" t="n">
-        <v>122902.86</v>
+        <v>140422.7</v>
       </c>
       <c r="E2" t="n">
-        <v>97.22</v>
+        <v>98.15000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/llm_stats/token_usage.xlsx
+++ b/llm_stats/token_usage.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX10"/>
+  <dimension ref="A1:AX15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2646,6 +2646,1209 @@
       </c>
       <c r="AX10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>9f4a0849-59dd-4f6b-8716-379d3acb3828</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-03-13 10:52:29</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>386</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Lexicographical Numbers</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/problems/lexicographical-numbers/</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>a6fabc3fd481f4004bf7fe96513f7d263b7eee8de60447b59d039e143bfebe96</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>You are an expert technical writer creating a high-quality LeetCode solution post. Problem Details: Number: 386 Name: Lexicographical Numbers Difficulty: medium Link: https://leetcode.com/problems/lexicographical-numbers/ Python Solution: class Solution: def lexicalOrder(self,...</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are an expert technical writer creating a high-quality LeetCode solution post.
+Problem Details:
+Number: 386
+Name: Lexicographical Numbers
+Difficulty: medium
+Link: https://leetcode.com/problems/lexicographical-numbers/
+Python Solution:
+class Solution:
+    def lexicalOrder(self, n: int) -&gt; List[int]:
+        list_strings = [str(i) for i in range(1,n+1)]
+        list_strings.sort()
+        return [int(i) for i in list_strings]
+Instructions:
+1. Generate a strong, descriptive, professional Title.
+- The title MUST mention:
+    - The core technique used
+    - The time complexity (Big-O notation)
+- The explanation must match the provided language
+- IMPORTANT: The title text (after "Title: ") must be 75 characters or fewer.
+2. Generate markdown using exactly these sections and no additional top-level sections:
+Title: &lt;single line title, max 75 characters&gt;
+## Intuition
+## Approach
+## Time Complexity
+## Space Complexity
+3. Do NOT include any code block and do NOT add a ## Code section.
+4. Keep the response concise, technical, and ready for markdown publishing.
+</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>1077</v>
+      </c>
+      <c r="O11" t="n">
+        <v>34</v>
+      </c>
+      <c r="P11" t="n">
+        <v>192</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>07effc72e412c4d5187980e72f51b74e57483a57ec56b216e94aeb0f1ca1dbb5</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>class Solution:
+    def lexicalOrder(self, n: int) -&gt; List[int]:
+        list_strings = [str(i) for i in range(1,n+1)]
+        list_strings.sort()
+        return [int(i) for i in list_strings]</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>315</v>
+      </c>
+      <c r="U11" t="n">
+        <v>219</v>
+      </c>
+      <c r="V11" t="n">
+        <v>534</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.6952</v>
+      </c>
+      <c r="X11" t="n">
+        <v>66599.82000000001</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>6038.44</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>23983.45</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>36418.09</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>6.0135</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>200</v>
+      </c>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>922</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Title: Efficient Lexicographical Number Generation in Python (O(n log n))
+## Intuition
+The problem asks to generate lexicographically sorted numbers within a given range. In this solution, we convert each number into a string, sort the strings, and then convert them back to integers. This method works because when converting integers to strings in ascending order, their lexicographical order is preserved.
+## Approach
+First, we create a list of strings using the range from 1 to n. Then, we sort this list of strings. Finally, we convert each sorted string back into an integer and collect them in a new list.
+## Time Complexity
+The time complexity is O(n log n) due to the string sort operation. The sort operation requires n log n comparisons for n elements.
+## Space Complexity
+The space complexity is O(n) as we need additional memory to store both the sorted list of strings and the final list of integers.</t>
+        </is>
+      </c>
+      <c r="AL11" t="n">
+        <v>1215</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>100</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ee83f2b0-2ab2-4cc1-9435-5256a5091275</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-03-14 10:20:51</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>566</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Reshape the Matrix</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/problems/reshape-the-matrix/description/</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>81801d67a4b92b923709d447133d9c4799eccc8bdc0f0245095dfc0688ea330e</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>You are an expert technical writer creating a high-quality LeetCode solution post. Problem Details: Number: 566 Name: Reshape the Matrix Difficulty: easy Link: https://leetcode.com/problems/reshape-the-matrix/description/ Python Solution: class Solution: def matrixReshape(self...</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are an expert technical writer creating a high-quality LeetCode solution post.
+Problem Details:
+Number: 566
+Name: Reshape the Matrix
+Difficulty: easy
+Link: https://leetcode.com/problems/reshape-the-matrix/description/
+Python Solution:
+class Solution:
+    def matrixReshape(self, mat: List[List[int]], r: int, c: int) -&gt; List[List[int]]:
+        presRows = len(mat)
+        presCols = len(mat[0])
+        if presRows*presCols != r*c:
+            return mat
+        result = [[0]*c for _ in range(r)]
+        presRow,presCol = 0,0
+        def next_index(i:int,j:int):
+            nonlocal presCols
+            if j == presCols-1:
+                return [i+1,0]
+            return [i,j+1]
+        for i in range(r):
+            for j in range(c):
+                result[i][j] = mat[presRow][presCol]
+                presRow,presCol = next_index(presRow,presCol)
+        return result
+Instructions:
+1. Generate a strong, descriptive, professional Title.
+- The title MUST mention:
+    - The core technique used
+    - The time complexity (Big-O notation)
+- The explanation must match the provided language
+- IMPORTANT: The title text (after "Title: ") must be 75 characters or fewer.
+2. Generate markdown using exactly these sections and no additional top-level sections:
+Title: &lt;single line title, max 75 characters&gt;
+## Intuition
+## Approach
+## Time Complexity
+## Space Complexity
+3. Do NOT include any code block and do NOT add a ## Code section.
+4. Keep the response concise, technical, and ready for markdown publishing.
+</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>1554</v>
+      </c>
+      <c r="O12" t="n">
+        <v>55</v>
+      </c>
+      <c r="P12" t="n">
+        <v>669</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>26</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>d47ee78c0c0be0c30966e64b06e4aea8c20f404b066eaef8e4602fdae39f6400</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>class Solution:
+    def matrixReshape(self, mat: List[List[int]], r: int, c: int) -&gt; List[List[int]]:
+        presRows = len(mat)
+        presCols = len(mat[0])
+        if presRows*presCols != r*c:
+            return mat
+        result = [[0]*c for _ in range(r)]
+        presRow,presCol = 0,0
+        def next_index(i:int,j:int):
+            nonlocal presCols
+            if j == presCols-1:
+                return [i+1,0]
+            return [i,j+1]
+        for i in range(r):
+            for j in range(c):
+                result[i][j] = mat[presRow][presCol]
+                presRow,presCol = next_index(presRow,presCol)
+        return result</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>476</v>
+      </c>
+      <c r="U12" t="n">
+        <v>318</v>
+      </c>
+      <c r="V12" t="n">
+        <v>794</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.6681</v>
+      </c>
+      <c r="X12" t="n">
+        <v>98843.33</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>8401.07</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>38443.44</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>51235.29</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>6.2067</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>200</v>
+      </c>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1377</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Title: Matrix Reshaping using Python with O(n) Time Complexity
+## Intuition
+The problem asks to reshape a given matrix while maintaining the original data structure. The intuitive approach is to traverse the matrix in a specific manner such that we can populate the new matrix with the correct values without causing any data loss.
+## Approach
+In this solution, we first check if it's possible to reshape the matrix as required by verifying that the number of elements (`presRows * presCols`) equals the desired new product (`r * c`). If not, the function returns the original matrix.
+If possible, we initialize a new matrix with dimensions `r` and `c`, then traverse the original matrix using nested loops to populate the new one. To avoid traversing the original matrix twice, we use a helper function called `next_index()` to determine the next index position in the original matrix.
+## Time Complexity
+Time complexity is O(n) where n equals the total number of elements in the input matrix. This is because we traverse each element once and perform basic arithmetic operations on it.
+## Space Complexity
+The space complexity is O(c) for the new matrix since its size depends on the desired columns (c). In the worst case, when the original matrix has a single row or column, the space complexity becomes linear with respect to the number of elements in the matrix.</t>
+        </is>
+      </c>
+      <c r="AL12" t="n">
+        <v>2147</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>52</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>b3b02607-f9dd-4205-b2d4-82f6766523f1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-03-14 10:22:09</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>563</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Binary Tree Tilt</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/problems/binary-tree-tilt/description/</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>97429269d8fb6a804581d3a580f8ed076c90c19deeb0f8f107671bf57c5aa29e</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>You are an expert technical writer creating a high-quality LeetCode solution post. Problem Details: Number: 563 Name: Binary Tree Tilt Difficulty: easy Link: https://leetcode.com/problems/binary-tree-tilt/description/ Python Solution: # Definition for a binary tree node. # cla...</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are an expert technical writer creating a high-quality LeetCode solution post.
+Problem Details:
+Number: 563
+Name: Binary Tree Tilt
+Difficulty: easy
+Link: https://leetcode.com/problems/binary-tree-tilt/description/
+Python Solution:
+# Definition for a binary tree node.
+# class TreeNode:
+#     def __init__(self, val=0, left=None, right=None):
+#         self.val = val
+#         self.left = left
+#         self.right = right
+class Solution:
+    def findTilt(self, root: Optional[TreeNode]) -&gt; int:
+        self.total_tilt = 0
+        def dfs(root):
+            if not root:
+                return 0
+            left_sum = dfs(root.left)
+            right_sum = dfs(root.right)
+            total_tilt = abs(left_sum-right_sum)
+            self.total_tilt += total_tilt
+            return root.val+left_sum+right_sum
+        dfs(root)
+        return self.total_tilt
+Instructions:
+1. Generate a strong, descriptive, professional Title.
+- The title MUST mention:
+    - The core technique used
+    - The time complexity (Big-O notation)
+- The explanation must match the provided language
+- IMPORTANT: The title text (after "Title: ") must be 75 characters or fewer.
+2. Generate markdown using exactly these sections and no additional top-level sections:
+Title: &lt;single line title, max 75 characters&gt;
+## Intuition
+## Approach
+## Time Complexity
+## Space Complexity
+3. Do NOT include any code block and do NOT add a ## Code section.
+4. Keep the response concise, technical, and ready for markdown publishing.
+</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>1524</v>
+      </c>
+      <c r="O13" t="n">
+        <v>53</v>
+      </c>
+      <c r="P13" t="n">
+        <v>643</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>24</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>5bf02b884d4c46fe9a7b13317dccf678b8a10522c79446273b0c17a9fc130616</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t># Definition for a binary tree node.
+# class TreeNode:
+#     def __init__(self, val=0, left=None, right=None):
+#         self.val = val
+#         self.left = left
+#         self.right = right
+class Solution:
+    def findTilt(self, root: Optional[TreeNode]) -&gt; int:
+        self.total_tilt = 0
+        def dfs(root):
+            if not root:
+                return 0
+            left_sum = dfs(root.left)
+            right_sum = dfs(root.right)
+            total_tilt = abs(left_sum-right_sum)
+            self.total_tilt += total_tilt
+            return root.val+left_sum+right_sum
+        dfs(root)
+        return self.total_tilt</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>455</v>
+      </c>
+      <c r="U13" t="n">
+        <v>265</v>
+      </c>
+      <c r="V13" t="n">
+        <v>720</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.5824</v>
+      </c>
+      <c r="X13" t="n">
+        <v>177060.99</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>8413.58</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>34816.06</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>42468.59</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>6.2399</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>200</v>
+      </c>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1044</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Title: Depth-First Search with Tilt Calculation in Binary Tree (O(N))
+## Intuition
+The approach is to traverse the binary tree using depth-first search (DFS). As we visit each node, we calculate the sum of values from that node down to the leaves on both sides. The difference between the sums of the left and right subtrees gives us the tilt for that node. By summing up all the tilts, we get the total tilt of the binary tree.
+## Approach
+The given solution defines a recursive DFS function `dfs` that visits each node in the binary tree. The function calculates the tilt for each node and also keeps track of the total tilt for the entire tree through the `total_tilt` variable in the outer scope.
+## Time Complexity
+The time complexity is O(N) where N is the number of nodes in the binary tree since we visit every node exactly once during DFS traversal.
+## Space Complexity
+The space complexity is O(H) where H is the maximum height (depth) of the binary tree because we use a recursive stack for DFS that has a maximum depth of H.</t>
+        </is>
+      </c>
+      <c r="AL13" t="n">
+        <v>1788</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>aee39860-0b47-4cca-9ba4-235adeeab9b8</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-03-14 19:07:50</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1584</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Min Cost to Connect All Points</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/problems/min-cost-to-connect-all-points/description</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fef77b8821b3fca112ec88b93a5754a95f1342920b844adbe014b1e76abfd730</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>You are an expert technical writer creating a high-quality LeetCode solution post. Problem Details: Number: 1584 Name: Min Cost to Connect All Points Difficulty: medium Link: https://leetcode.com/problems/min-cost-to-connect-all-points/description Python Solution: class Soluti...</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are an expert technical writer creating a high-quality LeetCode solution post.
+Problem Details:
+Number: 1584
+Name: Min Cost to Connect All Points
+Difficulty: medium
+Link: https://leetcode.com/problems/min-cost-to-connect-all-points/description
+Python Solution:
+class Solution:
+    def minCostConnectPoints(self, points: List[List[int]]) -&gt; int:
+        length = len(points)
+        min_dist = [float('inf')]*length
+        min_dist[0] = 0
+        visited = [False]*length
+        result = 0
+        for _ in range(length):
+            u = -1
+            for i in range(length):
+                if not visited[i] and (u == -1 or min_dist[i] &lt; min_dist[u]):
+                    u = i
+            result += min_dist[u]
+            visited[u] = True
+            for v in range(length):
+                if not visited[v]:
+                    dist = (abs(points[v][1] - points[u][1]) + abs(points[v][0]-points[u][0]))
+                    min_dist[v] = min(dist, min_dist[v])
+        return result 
+Instructions:
+1. Generate a strong, descriptive, professional Title.
+- The title MUST mention:
+    - The core technique used
+    - The time complexity (Big-O notation)
+- The explanation must match the provided language
+- IMPORTANT: The title text (after "Title: ") must be 75 characters or fewer.
+2. Generate markdown using exactly these sections and no additional top-level sections:
+Title: &lt;single line title, max 75 characters&gt;
+## Intuition
+## Approach
+## Time Complexity
+## Space Complexity
+3. Do NOT include any code block and do NOT add a ## Code section.
+4. Keep the response concise, technical, and ready for markdown publishing.
+</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>1658</v>
+      </c>
+      <c r="O14" t="n">
+        <v>57</v>
+      </c>
+      <c r="P14" t="n">
+        <v>747</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>28</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>4a7d67f430ca9e0990a562f5f6808194fe752c5b65c79ff06068efef14661b63</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">class Solution:
+    def minCostConnectPoints(self, points: List[List[int]]) -&gt; int:
+        length = len(points)
+        min_dist = [float('inf')]*length
+        min_dist[0] = 0
+        visited = [False]*length
+        result = 0
+        for _ in range(length):
+            u = -1
+            for i in range(length):
+                if not visited[i] and (u == -1 or min_dist[i] &lt; min_dist[u]):
+                    u = i
+            result += min_dist[u]
+            visited[u] = True
+            for v in range(length):
+                if not visited[v]:
+                    dist = (abs(points[v][1] - points[u][1]) + abs(points[v][0]-points[u][0]))
+                    min_dist[v] = min(dist, min_dist[v])
+        return result 
+        </t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>494</v>
+      </c>
+      <c r="U14" t="n">
+        <v>431</v>
+      </c>
+      <c r="V14" t="n">
+        <v>925</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.8725000000000001</v>
+      </c>
+      <c r="X14" t="n">
+        <v>112896.48</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>5545.72</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>33116.79</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>73999.8</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>5.8243</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>200</v>
+      </c>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1761</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Title: Union Find Algorithm with Prim's Minimum Spanning Tree Approach (O(n^2 + m))
+## Intuition
+This solution uses a combination of Depth-First Search (DFS) for exploring the graph and the Union-Find data structure to maintain connected components. The goal is to find the minimum cost of connecting all points in a 2D plane, where each point has a unique x-y coordinate pair. Prim's algorithm constructs a Minimum Spanning Tree (MST), adding edges incrementally that connect disjoint parts of the graph at minimum cost.
+## Approach
+1. Initialize an array `min_dist` to store the minimum distance from each point to any visited point, and a boolean array `visited` to keep track of which points have been explored.
+2. Start with an arbitrary unvisited point (u) and set its minimum distance to 0.
+3. Repeatedly find an unvisited point with the minimum distance from all visited points (u). Update the total cost by adding the current minimum distance.
+4. Mark the found point as visited, and update the distances of all other unvisited points reachable from the current point (u) using Euclidean distance.
+5. Continue this process until all points have been visited and connected in a MST.
+## Time Complexity
+The time complexity for finding the minimum spanning tree is O(n^2 + m), where n is the number of points, and m is the total number of edges (in our case, approximately 2n edges). This happens because we perform DFS operations and edge updates logarithmic in the number of connected components (in this case, log n) for each point.
+## Space Complexity
+The space complexity is O(n), as we need to store the points' coordinates, minimum distances, and visited statuses, requiring constant space per point (O(1)) and linear space in total (O(n)).</t>
+        </is>
+      </c>
+      <c r="AL14" t="n">
+        <v>2608</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>56</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>9410027a-cd4f-4970-9c8d-dd7b03f37899</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-03-14 19:44:09</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1670</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Design Front Middle Back Queue</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/problems/design-front-middle-back-queue/description</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>a916a49614b06647ead3d7e61df7d647b73946d3b1572b59cca3a9f2ae1f92a2</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>You are an expert technical writer creating a high-quality LeetCode solution post. Problem Details: Number: 1670 Name: Design Front Middle Back Queue Difficulty: medium Link: https://leetcode.com/problems/design-front-middle-back-queue/description Python Solution: class FrontM...</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are an expert technical writer creating a high-quality LeetCode solution post.
+Problem Details:
+Number: 1670
+Name: Design Front Middle Back Queue
+Difficulty: medium
+Link: https://leetcode.com/problems/design-front-middle-back-queue/description
+Python Solution:
+class FrontMiddleBackQueue:
+    def __init__(self):
+        self.arr = []
+    def pushFront(self, val: int) -&gt; None:
+        self.arr.insert(0, val)
+    def pushMiddle(self, val: int) -&gt; None:
+        mid = len(self.arr) // 2
+        self.arr.insert(mid, val)
+    def pushBack(self, val: int) -&gt; None:
+        self.arr.append(val)
+    def popFront(self) -&gt; int:
+        if not self.arr:
+            return -1
+        return self.arr.pop(0)
+    def popMiddle(self) -&gt; int:
+        if not self.arr:
+            return -1
+        mid = (len(self.arr) - 1) // 2
+        return self.arr.pop(mid)
+    def popBack(self) -&gt; int:
+        if not self.arr:
+            return -1
+        return self.arr.pop()
+Instructions:
+1. Generate a strong, descriptive, professional Title.
+- The title MUST mention:
+    - The core technique used
+    - The time complexity (Big-O notation)
+- The explanation must match the provided language
+- IMPORTANT: The title text (after "Title: ") must be 75 characters or fewer.
+2. Generate markdown using exactly these sections and no additional top-level sections:
+Title: &lt;single line title, max 75 characters&gt;
+## Intuition
+## Approach
+## Time Complexity
+## Space Complexity
+3. Do NOT include any code block and do NOT add a ## Code section.
+4. Keep the response concise, technical, and ready for markdown publishing.
+</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>1616</v>
+      </c>
+      <c r="O15" t="n">
+        <v>60</v>
+      </c>
+      <c r="P15" t="n">
+        <v>705</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>31</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>3692881eba02de06d7c1bde97bcba3396929278c51ea97143a90767458387eac</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>class FrontMiddleBackQueue:
+    def __init__(self):
+        self.arr = []
+    def pushFront(self, val: int) -&gt; None:
+        self.arr.insert(0, val)
+    def pushMiddle(self, val: int) -&gt; None:
+        mid = len(self.arr) // 2
+        self.arr.insert(mid, val)
+    def pushBack(self, val: int) -&gt; None:
+        self.arr.append(val)
+    def popFront(self) -&gt; int:
+        if not self.arr:
+            return -1
+        return self.arr.pop(0)
+    def popMiddle(self) -&gt; int:
+        if not self.arr:
+            return -1
+        mid = (len(self.arr) - 1) // 2
+        return self.arr.pop(mid)
+    def popBack(self) -&gt; int:
+        if not self.arr:
+            return -1
+        return self.arr.pop()</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>499</v>
+      </c>
+      <c r="U15" t="n">
+        <v>487</v>
+      </c>
+      <c r="V15" t="n">
+        <v>986</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="X15" t="n">
+        <v>149945.24</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>8144.38</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>41112.68</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>99983.14</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>4.8708</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>200</v>
+      </c>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1850</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Title: Efficient Dynamic Array Queue Implementation (Python - O(1) Avg for all operations except pushFront and popFront - O(n))
+## Intuition
+The problem requires implementing a queue with three functions: `pushFront`, `pushMiddle`, `popFront`, `popMiddle`, and `popBack`. To achieve this, we use a dynamic array as our data structure, which allows for efficient insertion and deletion at the end (O(1) time complexity). We also implement special logic for `pushFront` and `popFront` to ensure their O(n) worst-case time complexity doesn't affect average-case performance.
+## Approach
+Upon initialization, we create an empty array. The `pushFront`, `pushMiddle`, and `pushBack` functions all insert elements at the respective positions in the array using the `insert()` method. However, `pushFront` requires moving all elements to make space for the new element, hence its O(n) worst-case time complexity.
+The `popFront`, `popMiddle`, and `popBack` functions remove elements from the array using the `pop()` or `pop(index)` method. To implement `popFront`, we first check if the queue is empty, then remove the element at index 0. For `popMiddle`, we find the middle index of the array (rounding down for even-length arrays), and remove the element at that index. Lastly, `popBack` simply removes the last element from the array using the `pop()` method.
+## Time Complexity
+- `pushFront`: O(n) - Worst case when the queue is empty or nearly full
+- `pushMiddle`, `pushBack`, `popFront`, `popMiddle`, and `popBack`: O(1) - Average case; O(1) for most common operations
+## Space Complexity
+The data structure requires constant space (O(n)) to store the elements in the array. In the worst-case scenario, when all three queues (front, middle, and back) are full, the space requirement is linear with the total number of items in the queue (O(n)).</t>
+        </is>
+      </c>
+      <c r="AL15" t="n">
+        <v>2611</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>58</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>100</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>2409</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2679,7 +3882,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -2689,7 +3892,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -2719,7 +3922,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.64</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="7">
@@ -2729,7 +3932,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>140422.7</v>
+        <v>133510.72</v>
       </c>
     </row>
     <row r="8">
@@ -2739,7 +3942,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>98.15000000000001</v>
+        <v>98.81</v>
       </c>
     </row>
     <row r="9">
@@ -2749,7 +3952,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>97.78</v>
+        <v>98.56999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2763,7 +3966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3045,7 +4248,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>bc4d6a1b30057aeb421828e3058b67b393c68ef3e9a044f87d681c404bd8d7c3</t>
+          <t>81801d67a4b92b923709d447133d9c4799eccc8bdc0f0245095dfc0688ea330e</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -3058,10 +4261,10 @@
         <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>6.31</v>
+        <v>6.21</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9457</v>
+        <v>0.6681</v>
       </c>
     </row>
     <row r="9">
@@ -3082,23 +4285,208 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>97429269d8fb6a804581d3a580f8ed076c90c19deeb0f8f107671bf57c5aa29e</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H9" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.5824</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>a6fabc3fd481f4004bf7fe96513f7d263b7eee8de60447b59d039e143bfebe96</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>100</v>
+      </c>
+      <c r="G10" t="n">
+        <v>100</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.6952</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>a916a49614b06647ead3d7e61df7d647b73946d3b1572b59cca3a9f2ae1f92a2</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>100</v>
+      </c>
+      <c r="G11" t="n">
+        <v>100</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.976</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>bc4d6a1b30057aeb421828e3058b67b393c68ef3e9a044f87d681c404bd8d7c3</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>100</v>
+      </c>
+      <c r="G12" t="n">
+        <v>100</v>
+      </c>
+      <c r="H12" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.9457</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>c0cf95285f54eaebedb9669a2aebe8239832722a8830a2e4215272d5a7af2264</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>100</v>
-      </c>
-      <c r="G9" t="n">
-        <v>100</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>100</v>
+      </c>
+      <c r="G13" t="n">
+        <v>100</v>
+      </c>
+      <c r="H13" t="n">
         <v>4.64</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I13" t="n">
         <v>1.1983</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>analysis_only_append_code_v1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>fef77b8821b3fca112ec88b93a5754a95f1342920b844adbe014b1e76abfd730</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>100</v>
+      </c>
+      <c r="G14" t="n">
+        <v>100</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.8725000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -3149,16 +4537,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>5.64</v>
+        <v>5.71</v>
       </c>
       <c r="D2" t="n">
-        <v>140422.7</v>
+        <v>133510.72</v>
       </c>
       <c r="E2" t="n">
-        <v>98.15000000000001</v>
+        <v>98.81</v>
       </c>
     </row>
   </sheetData>
